--- a/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>BHP</t>
   </si>
@@ -656,244 +656,256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15429000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>15429000</v>
+      </c>
+      <c r="F8" s="3">
         <v>13951000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>13951000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13043000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>13043000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>12588000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>12588000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>14213000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>14213000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>13616000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>13616000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>14100000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>14100000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>12992000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>24044000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>38924000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>22294000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>23546000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20742000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>22603000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>20526000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>16944000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>18796000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>12855000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>15712000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>19776000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>24860000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>-3837000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-3837000</v>
+      </c>
+      <c r="F9" s="3">
         <v>7973500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7973500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>-3407500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>-3407500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>7966500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>7966500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>-3249000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>-3249000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8214000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>8214000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>-2206000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7680500</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>5</v>
@@ -928,55 +940,61 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>19266000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>19266000</v>
+      </c>
+      <c r="F10" s="3">
         <v>5977500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5977500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>16450500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>16450500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4621500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4621500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>17462000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>17462000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5402000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5402000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>16306000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>16306000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5311500</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>5</v>
@@ -1011,8 +1029,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,8 +1066,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1125,8 +1151,14 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1208,64 +1240,70 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1136000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1136000</v>
+      </c>
+      <c r="F14" s="3">
         <v>34500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>34500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-102000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-102000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>214500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>214500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-271000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-271000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1758500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1853500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>165000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>165000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>146000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>395000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-489000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>40000</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
@@ -1279,11 +1317,11 @@
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1291,56 +1329,62 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3100500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3100500</v>
+      </c>
+      <c r="F15" s="3">
         <v>1460000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1460000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2770000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2770000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1324000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1324000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2647500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2647500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1314500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>1314500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2530500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2530500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1228000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1374,8 +1418,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1402,174 +1452,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8742000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8742000</v>
+      </c>
+      <c r="F17" s="3">
         <v>8269000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8269000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8126500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8126500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8195000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8195000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8244000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8244000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8453500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8453500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8379500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>8379500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7987000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>14550000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>25241000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13980000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>14766000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13409000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>13772000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>13361000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>10447000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>12739000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3021000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>22742000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>19036000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>16930000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6687000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6687000</v>
+      </c>
+      <c r="F18" s="3">
         <v>5682000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>5682000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>4916500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>4916500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>4393000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4393000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5969000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5969000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>5162500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5162500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>5720500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5720500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>5005000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9494000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>13683000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>8314000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>8780000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>7333000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>8831000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>7165000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>6497000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>6057000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>9834000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-7030000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>740000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>7930000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1599,423 +1663,455 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>57500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-217000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-217000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-228000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-228000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>145000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>145000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1270500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1175500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-96500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-96500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-343500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-210000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>52000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-38000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-10000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>41000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-27000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-130000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-295000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-72000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-175000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-140000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9730000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>9730000</v>
+      </c>
+      <c r="F21" s="3">
         <v>7359000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>7359000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>7586000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>7586000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>5945000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5945000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8471500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>8471500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>5206500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5301500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>8347500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>8347500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>6576500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>12529000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>19847000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>11290000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>11711000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>10262000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>11886000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>10241000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>8586000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>9785000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>11267000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2469000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>5357000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>12260000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F22" s="3">
         <v>211500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>211500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>216500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>216500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>233000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>233000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>245000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>245000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>314000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>314000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>210500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>210500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>217500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>271000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>910000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>486000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>521000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>574000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>560000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>528000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>545000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>505000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>409000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>388000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>240000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5429500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5429500</v>
+      </c>
+      <c r="F23" s="3">
         <v>5777500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>5777500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>4842000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4842000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>4334500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4334500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>6033000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>6033000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1991000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1991000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>5610000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>5610000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>5090500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>9013000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>12825000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>7790000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>8249000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>6800000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>8244000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>6507000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>5657000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>5480000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>9250000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-7459000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>360000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>7696000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2478500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2478500</v>
+      </c>
+      <c r="F24" s="3">
         <v>2215500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2215500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1913000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1913000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1692000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1692000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2085500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2085500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1138000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1138000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2011000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2011000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1527500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>3993000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4197000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2600000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>3171000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2358000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2906000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1781000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>2415000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2028000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>3829000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-1726000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>362000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>3304000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2097,174 +2193,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2951000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2951000</v>
+      </c>
+      <c r="F26" s="3">
         <v>3562000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3562000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2929000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2929000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2642500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2642500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3947500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3947500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>853000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>853000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3599000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3599000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>3563000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>5020000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>8628000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>5190000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5078000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>4442000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>5338000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>4726000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3242000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3452000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>5421000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-5733000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>4392000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="F27" s="3">
         <v>2820000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2820000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2301500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2301500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2208000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2208000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3485000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3485000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>463500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>463500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3232000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3232000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3228500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4068000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>7848000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>4868000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>4584000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>4057000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>4779000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>4167000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3158000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3204000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>5179000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-5669000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-442000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3864000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2346,8 +2460,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2391,46 +2511,52 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-192000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>108000</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-42000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-293000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-6010000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-2152000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>-472000</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-5895000</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1913000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2512,8 +2638,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2595,174 +2727,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="F32" s="3">
         <v>217000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>217000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>228000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>228000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-145000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-145000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1270500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1175500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>96500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>96500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>343500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>210000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-52000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>38000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>10000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-41000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>27000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>130000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>295000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>72000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>175000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>41000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>140000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="F33" s="3">
         <v>2820000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2820000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2301500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2301500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2208000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2208000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3485000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3485000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>463500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>463500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3232000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3232000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3228500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3876000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>7956000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>4868000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>4542000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3764000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1231000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2015000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2686000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3204000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-716000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-5669000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2355000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2844,179 +2994,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="F35" s="3">
         <v>2820000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2820000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2301500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2301500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2208000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2208000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3485000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3485000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>463500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>463500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3232000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3232000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3228500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3876000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>7956000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>4868000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>4542000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3764000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1231000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2015000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2686000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3204000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-716000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-5669000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2355000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3046,8 +3214,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3077,755 +3247,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18532000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18532000</v>
+      </c>
+      <c r="F41" s="3">
         <v>13466000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13466000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11894000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11894000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9560000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9560000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12501000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12501000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10319000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10319000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12428000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12428000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9605000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9291000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>13426000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>14321000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>15613000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>15575000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>15871000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>12322000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>14153000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>13987000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>10319000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10626000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>6753000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>6130000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>43000</v>
+        <v>29000</v>
       </c>
       <c r="E42" s="3">
-        <v>43000</v>
+        <v>29000</v>
       </c>
       <c r="F42" s="3">
-        <v>50000</v>
+        <v>72000</v>
       </c>
       <c r="G42" s="3">
-        <v>50000</v>
+        <v>72000</v>
       </c>
       <c r="H42" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I42" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J42" s="3">
         <v>28000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>28000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>29000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>29000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>326000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>326000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>63000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>63000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>329000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>227000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>84000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>54000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>87000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>237000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>200000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>51000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>72000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>103000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>121000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>75000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>83000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5044000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5044000</v>
+      </c>
+      <c r="F43" s="3">
         <v>5871000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5871000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4661000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4661000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5036000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5036000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5483000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5483000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5798000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5798000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5102000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5102000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4962000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4868000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3730000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3732000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3586000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>6487000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3202000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3639000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3031000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>3781000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3722000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3579000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>4979000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>6214000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6591000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6591000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5817000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5817000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5538000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5538000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5533000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5533000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5828000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5828000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5313000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5313000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5220000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5220000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>4912000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4511000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>4101000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3939000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3840000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3972000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3764000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4020000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3673000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3499000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3411000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3914000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>4292000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>6149000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>837000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>837000</v>
+      </c>
+      <c r="F45" s="3">
         <v>702000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>702000</v>
       </c>
-      <c r="F45" s="3">
-        <v>687000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>687000</v>
-      </c>
       <c r="H45" s="3">
+        <v>724000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>724000</v>
+      </c>
+      <c r="J45" s="3">
         <v>698000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>698000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>497000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>497000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2044000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2044000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>538000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>538000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>295000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>113000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>130000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>247000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>136000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>12093000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>111000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>127000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>131000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>141000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>189000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>262000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31033000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>31033000</v>
+      </c>
+      <c r="F46" s="3">
         <v>25928000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>25928000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22830000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>22830000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>20855000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>20855000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>24338000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>24338000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23800000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>23800000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>23351000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>23351000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>20103000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>19010000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>21471000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>22246000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>23373000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>26407000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>35130000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>20143000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>21056000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>21501000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>17714000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>18383000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>16369000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>18901000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4815000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4815000</v>
+      </c>
+      <c r="F47" s="3">
         <v>4910000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>4910000</v>
       </c>
-      <c r="F47" s="3">
-        <v>4758000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>4758000</v>
-      </c>
       <c r="H47" s="3">
+        <v>4619000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4619000</v>
+      </c>
+      <c r="J47" s="3">
         <v>2435000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2435000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2195000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2195000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2489000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2489000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2507000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2507000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2412000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4633000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5374000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4156000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>4185000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>3663000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>3652000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>4276000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>4532000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>4460000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>6122000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>5054000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>6370000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>7416000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80046000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>80046000</v>
+      </c>
+      <c r="F48" s="3">
         <v>79851000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>79851000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>76457000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>76457000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>73112000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>73112000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>71629000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>71629000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>69994000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>69994000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>71818000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>71818000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>62178000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>73711000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>72362000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>70196000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>68041000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>66673000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>67182000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>78849000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>80497000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>82170000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>83975000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>85439000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>94072000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>108771000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2113000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2113000</v>
+      </c>
+      <c r="F49" s="3">
         <v>2012000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2012000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1924000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1924000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1761000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1761000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1718000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1718000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1615000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1615000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1610000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1610000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1397000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1508000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1574000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>670000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>675000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>718000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>778000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3873000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3968000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4030000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4119000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4214000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>4292000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>5289000</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3907,8 +4133,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3990,91 +4222,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3031000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3031000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2980000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2980000</v>
       </c>
-      <c r="F52" s="3">
-        <v>2459000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2459000</v>
-      </c>
       <c r="H52" s="3">
+        <v>2598000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2598000</v>
+      </c>
+      <c r="J52" s="3">
         <v>2201000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2201000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2108000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2108000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1845000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1845000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1806000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1806000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1533000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4371000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4952000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5022000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>4587000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>4953000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>5251000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5441000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6953000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>7374000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>7023000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>5579000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3477000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>5704000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4156,91 +4400,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>121387000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>121387000</v>
+      </c>
+      <c r="F54" s="3">
         <v>116012000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>116012000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>108790000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>108790000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>100722000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>100722000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>102362000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>102362000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>99988000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>99988000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>101296000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>101296000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>87824000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>103233000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>105733000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>102290000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>100861000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>102414000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>111993000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>112582000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>117006000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>119535000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>118953000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>118669000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>124580000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>146081000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4270,8 +4526,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4301,506 +4559,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7579000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7579000</v>
+      </c>
+      <c r="F57" s="3">
         <v>6288000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6288000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6637000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6637000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6032000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6032000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6719000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6719000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6092000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6092000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6296000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6296000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>4882000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5663000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5767000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5798000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>6717000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5616000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5977000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5999000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5551000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>5128000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>5389000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5678000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>7389000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>8338000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2684000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2684000</v>
+      </c>
+      <c r="F58" s="3">
         <v>3431000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3431000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2018000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2018000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>491000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>491000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2260000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2260000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3155000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3155000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7320000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7320000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2220000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3560000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>10024000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4273000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1661000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1527000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2736000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2033000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1241000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3374000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4653000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>4071000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3201000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6202000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6202000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6007000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6007000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6984000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6984000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5774000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5774000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5317000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5317000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5928000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5928000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5427000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5427000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4787000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4138000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4045000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3691000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3961000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3225000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5276000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3498000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>4574000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3497000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2298000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1889000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2263000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2553000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16465000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>16465000</v>
+      </c>
+      <c r="F60" s="3">
         <v>15726000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15726000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15639000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>15639000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12297000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>12297000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14296000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14296000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>15175000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>15175000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>19043000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>19043000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11889000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>13361000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>14824000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>13762000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>12339000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10368000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13989000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11530000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>11366000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11999000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>12340000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>11638000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>12853000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>13350000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25743000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>25743000</v>
+      </c>
+      <c r="F61" s="3">
         <v>25765000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>25765000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>23534000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>23534000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>21220000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>21220000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>19971000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>19971000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>20790000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>20790000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>16780000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>16780000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>14711000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>19159000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>22036000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>22535000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>23167000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>23938000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>24069000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>25700000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>29233000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>30670000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>31768000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>32476000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>27969000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>28610000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19721000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>19721000</v>
+      </c>
+      <c r="F62" s="3">
         <v>15250000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>15250000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>13842000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>13842000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>14023000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>14023000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>15595000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15595000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>15057000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>15057000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>12594000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>12594000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>11255000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>17290000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>16698000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>13575000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>13531000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>12792000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>13265000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>13191000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>13681000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>14441000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>14774000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>13125000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>13213000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>17871000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4882,8 +5178,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4965,8 +5267,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5048,91 +5356,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>65066000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>65066000</v>
+      </c>
+      <c r="F66" s="3">
         <v>60547000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>60547000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>56572000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>56572000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>51125000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>51125000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>53242000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>53242000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>54397000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>54397000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>52766000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>52766000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>41272000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>54311000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>57868000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>54168000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>53621000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>51767000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>56401000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>55605000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>59748000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>62886000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>64663000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>62883000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>59812000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>66236000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5162,8 +5482,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5245,8 +5567,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5328,8 +5656,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5411,8 +5745,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5494,91 +5834,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>45721000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>45721000</v>
+      </c>
+      <c r="F72" s="3">
         <v>45255000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>45255000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>42670000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>42670000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>40612000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>40612000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>39963000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>39963000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>36632000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>36632000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>39787000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>39787000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>37912000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>46784000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>45702000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>45968000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>45104000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>48495000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>53354000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>54742000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>55018000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>54417000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>52080000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>53585000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>62601000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>77832000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5660,8 +6012,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5743,8 +6101,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5826,91 +6190,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50923000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>50923000</v>
+      </c>
+      <c r="F76" s="3">
         <v>50407000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>50407000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>47665000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>47665000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>45516000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>45516000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>44811000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>44811000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>41392000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>41392000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>44496000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>44496000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>42601000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>48922000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>47865000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>48122000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>47240000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>50647000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>55592000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>56977000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>57258000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>56649000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>54290000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>55786000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>64768000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>79845000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5992,179 +6368,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="F81" s="3">
         <v>2820000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2820000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2301500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2301500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2208000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2208000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3485000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3485000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>463500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>463500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3232000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3232000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3228500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3876000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>7956000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>4868000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>4542000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3764000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1231000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2015000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2686000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3204000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-716000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-5669000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2355000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>4265000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6194,91 +6588,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1390500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1390500</v>
+      </c>
+      <c r="F83" s="3">
         <v>1324000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1324000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="I83" s="3">
         <v>1279500</v>
       </c>
-      <c r="G83" s="3">
-        <v>1279500</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1314500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1314500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1302500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1255500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1228000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1228000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1416000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1386000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1425500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>3245000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>6112000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>3014000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2941000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>2888000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>2251000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>4037000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>3919000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>3800000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>4602000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>4757000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>4401000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6360,8 +6762,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6443,8 +6851,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6526,8 +6940,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6609,8 +7029,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6692,91 +7118,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6203000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6203000</v>
+      </c>
+      <c r="F89" s="3">
         <v>4686000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4686000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5187500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5187500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4158500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4158500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5890500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>5890500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4442000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4442000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5965500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>5965500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3385000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>9369000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>15706000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>7442000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>10597000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>7274000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>11118000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>7343000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>9107000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>7697000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>5365000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>5260000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>8873000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>10423000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6806,91 +7244,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2497000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2497000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2631500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2631500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2294500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2294500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2602500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2602500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2264500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2372000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2028000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1513500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-3614000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3845000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3795000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-476000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-397000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-410000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-464000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-527000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-439000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-342000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-410000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>807000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-13668000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6972,8 +7418,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7055,91 +7507,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2772500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2772500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3233000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3233000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3840500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3840500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1841500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2539500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4888000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1644500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-4209000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-7616000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-3732000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-723000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>3330000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3475000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2446000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2239000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1922000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-4038000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-6837000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-6317000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7169,91 +7633,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1838000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1838000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1540000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1540000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1269000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1269000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1932500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1932500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1815000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1815000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>2022500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>2022500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>2304000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>2304000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>4330000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-6876000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-3934000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-7984000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-3411000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-2944000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-2276000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-2173000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-748000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-864000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-3289000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-3209000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7335,8 +7807,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7418,8 +7896,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7501,253 +7985,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-725000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-725000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-350500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-350500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2635000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2635000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2843000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2991500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>298000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>298000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-5455500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-9595000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-9752000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-5000000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-9430000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-11098000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-3832000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-7059000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-7009000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-2454000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2738000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1517000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-6759000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>170500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>170500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-158500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-158500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-116500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-116500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>37000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>37000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>33500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>33500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-198000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-198000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>300000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-505000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>50000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-220000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-275000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>331000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>321000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2533000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2533000</v>
+      </c>
+      <c r="F102" s="3">
         <v>786500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>786500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1167000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1167000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1469500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1469500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1089500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1089500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1052000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1409000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1409000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3815500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-4135000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2167000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1272000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>494000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-714000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>3536000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>180000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3652000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-306000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>3969000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>495000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2634000</v>
       </c>
     </row>
